--- a/Excel/PCA_loadings_denorm_25.xlsx
+++ b/Excel/PCA_loadings_denorm_25.xlsx
@@ -631,79 +631,79 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>384.7808827916724</v>
+        <v>0.008703162039824906</v>
       </c>
       <c r="C4" t="n">
-        <v>888.1332909273641</v>
+        <v>0.01229200081059715</v>
       </c>
       <c r="D4" t="n">
-        <v>-573.4365118367524</v>
+        <v>-0.02405416274190306</v>
       </c>
       <c r="E4" t="n">
-        <v>-1076.468385097194</v>
+        <v>-0.03598758133998512</v>
       </c>
       <c r="F4" t="n">
-        <v>55.82301678185204</v>
+        <v>0.001231312692483133</v>
       </c>
       <c r="G4" t="n">
-        <v>-584.3095832152644</v>
+        <v>-0.00637036712925465</v>
       </c>
       <c r="H4" t="n">
-        <v>691.486813250625</v>
+        <v>0.0176517384798049</v>
       </c>
       <c r="I4" t="n">
-        <v>-1358.333816939466</v>
+        <v>-0.02508707673332754</v>
       </c>
       <c r="J4" t="n">
-        <v>598.5800355426038</v>
+        <v>0.005567251852169963</v>
       </c>
       <c r="K4" t="n">
-        <v>-56.53004745722014</v>
+        <v>-0.001928719510753461</v>
       </c>
       <c r="L4" t="n">
-        <v>646.63846922832</v>
+        <v>0.08923233959156833</v>
       </c>
       <c r="M4" t="n">
-        <v>-198.8515473093852</v>
+        <v>-0.001650479929697491</v>
       </c>
       <c r="N4" t="n">
-        <v>869.1194869871998</v>
+        <v>0.008751709520731964</v>
       </c>
       <c r="O4" t="n">
-        <v>357.3904091518201</v>
+        <v>0.005565985751212834</v>
       </c>
       <c r="P4" t="n">
-        <v>118.2370680610535</v>
+        <v>0.001868120932576317</v>
       </c>
       <c r="Q4" t="n">
-        <v>-197.2880587173654</v>
+        <v>-0.02289532780346492</v>
       </c>
       <c r="R4" t="n">
-        <v>15.21052086946689</v>
+        <v>0.001134039473122828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.07867077498348073</v>
+        <v>-1.659567001521541e-05</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.002547660615951988</v>
+        <v>-2.813280929987695e-06</v>
       </c>
       <c r="U4" t="n">
-        <v>4.962970325541498e-05</v>
+        <v>1.709169015769689e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>-6.611756780282345e-06</v>
+        <v>-1.219517489859632e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001186428257477316</v>
+        <v>3.808559060757363e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.364449940682659e-05</v>
+        <v>-3.484749401096376e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.665769813577727e-05</v>
+        <v>9.153302867821498e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1.231188764922602e-05</v>
+        <v>-5.321971166759398e-09</v>
       </c>
     </row>
     <row r="5">
@@ -713,79 +713,79 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44211.6188381819</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>-72252.94763743336</v>
+        <v>-1</v>
       </c>
       <c r="D5" t="n">
-        <v>-23839.38771802725</v>
+        <v>-1</v>
       </c>
       <c r="E5" t="n">
-        <v>-29912.21818792112</v>
+        <v>-1</v>
       </c>
       <c r="F5" t="n">
-        <v>45336.18237076423</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>91723.06263667888</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>15553.44702511428</v>
+        <v>0.3970363195448378</v>
       </c>
       <c r="I5" t="n">
-        <v>-54144.76271501792</v>
+        <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>-107518.0450672972</v>
+        <v>-1</v>
       </c>
       <c r="K5" t="n">
-        <v>-29309.62596792339</v>
+        <v>-1</v>
       </c>
       <c r="L5" t="n">
-        <v>-584.6426808418648</v>
+        <v>-0.0806772821587049</v>
       </c>
       <c r="M5" t="n">
-        <v>120481.0453804378</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>99308.53908351719</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>-64209.72405003811</v>
+        <v>-1</v>
       </c>
       <c r="P5" t="n">
-        <v>-63291.9775156062</v>
+        <v>-1</v>
       </c>
       <c r="Q5" t="n">
-        <v>4176.671104448953</v>
+        <v>0.4847037103275099</v>
       </c>
       <c r="R5" t="n">
-        <v>2125.726232182124</v>
+        <v>0.1584861870960821</v>
       </c>
       <c r="S5" t="n">
-        <v>156.6475456170145</v>
+        <v>0.03304493919500927</v>
       </c>
       <c r="T5" t="n">
-        <v>773.9362024898728</v>
+        <v>0.8546271610350503</v>
       </c>
       <c r="U5" t="n">
-        <v>2903.732913334219</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
-        <v>-5421.617020878781</v>
+        <v>-1</v>
       </c>
       <c r="W5" t="n">
-        <v>3115.163080184412</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-2113.337027438945</v>
+        <v>-1</v>
       </c>
       <c r="Y5" t="n">
-        <v>-692.6462155853501</v>
+        <v>-0.3806048434679033</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2313.407431841247</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -795,79 +795,79 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2749.72666570356</v>
+        <v>0.06219466144788278</v>
       </c>
       <c r="C6" t="n">
-        <v>-1851.395634629396</v>
+        <v>-0.02562380768075697</v>
       </c>
       <c r="D6" t="n">
-        <v>-642.2251233026815</v>
+        <v>-0.02693966518347421</v>
       </c>
       <c r="E6" t="n">
-        <v>317.4988233063198</v>
+        <v>0.01061435234631075</v>
       </c>
       <c r="F6" t="n">
-        <v>-3594.250799859967</v>
+        <v>-0.07927996165327272</v>
       </c>
       <c r="G6" t="n">
-        <v>1321.218886288974</v>
+        <v>0.01440443491864646</v>
       </c>
       <c r="H6" t="n">
-        <v>2516.887588624664</v>
+        <v>0.06424915218356722</v>
       </c>
       <c r="I6" t="n">
-        <v>20.81696139654773</v>
+        <v>0.0003844686051375716</v>
       </c>
       <c r="J6" t="n">
-        <v>2155.362475690724</v>
+        <v>0.02004651846433452</v>
       </c>
       <c r="K6" t="n">
-        <v>2009.176134612226</v>
+        <v>0.06855004348438562</v>
       </c>
       <c r="L6" t="n">
-        <v>2894.880520396142</v>
+        <v>0.3994766379755798</v>
       </c>
       <c r="M6" t="n">
-        <v>5266.616359454001</v>
+        <v>0.04371323591046073</v>
       </c>
       <c r="N6" t="n">
-        <v>-2496.475991570675</v>
+        <v>-0.02513858339483951</v>
       </c>
       <c r="O6" t="n">
-        <v>4051.041429537477</v>
+        <v>0.06309077775167719</v>
       </c>
       <c r="P6" t="n">
-        <v>2020.201714267548</v>
+        <v>0.03191876432948264</v>
       </c>
       <c r="Q6" t="n">
-        <v>8616.957154354801</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>139.2897280528527</v>
+        <v>0.01038492048813154</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6247799126623674</v>
+        <v>-0.0001317978787530307</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.003691570824266846</v>
+        <v>-4.076455763605758e-06</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0005637817306101899</v>
+        <v>1.941575714561247e-07</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0009066843303334153</v>
+        <v>1.672350383366718e-07</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002420426011326745</v>
+        <v>7.769821190816952e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0002978402092719407</v>
+        <v>-1.409336066159212e-07</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.972208488526998e-05</v>
+        <v>4.380679624886244e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0003583554481083666</v>
+        <v>1.549037334176585e-07</v>
       </c>
     </row>
     <row r="7">
@@ -877,79 +877,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-667.0211656087981</v>
+        <v>-0.01508701068038584</v>
       </c>
       <c r="C7" t="n">
-        <v>308.7173712433084</v>
+        <v>0.004272730474505454</v>
       </c>
       <c r="D7" t="n">
-        <v>220.8981274158725</v>
+        <v>0.009266099030254464</v>
       </c>
       <c r="E7" t="n">
-        <v>-146.2025605911623</v>
+        <v>-0.004887720451644756</v>
       </c>
       <c r="F7" t="n">
-        <v>320.5484716985508</v>
+        <v>0.007070477815645582</v>
       </c>
       <c r="G7" t="n">
-        <v>424.9629743428071</v>
+        <v>0.004633109297997534</v>
       </c>
       <c r="H7" t="n">
-        <v>-679.5475371388294</v>
+        <v>-0.01734696190919629</v>
       </c>
       <c r="I7" t="n">
-        <v>-526.2545489114353</v>
+        <v>-0.009719398932105213</v>
       </c>
       <c r="J7" t="n">
-        <v>175.8949402042061</v>
+        <v>0.001635957388307337</v>
       </c>
       <c r="K7" t="n">
-        <v>-639.185694974909</v>
+        <v>-0.02180804680600282</v>
       </c>
       <c r="L7" t="n">
-        <v>-857.7686900848988</v>
+        <v>-0.1183670794223114</v>
       </c>
       <c r="M7" t="n">
-        <v>315.0616332866624</v>
+        <v>0.002615030707044465</v>
       </c>
       <c r="N7" t="n">
-        <v>322.1121074080829</v>
+        <v>0.003243548947358805</v>
       </c>
       <c r="O7" t="n">
-        <v>216.527297293167</v>
+        <v>0.003372188566398899</v>
       </c>
       <c r="P7" t="n">
-        <v>1229.478423916145</v>
+        <v>0.01942550181202644</v>
       </c>
       <c r="Q7" t="n">
-        <v>469.9198899956673</v>
+        <v>0.05453431896875351</v>
       </c>
       <c r="R7" t="n">
-        <v>206.6983909390295</v>
+        <v>0.01541065794968065</v>
       </c>
       <c r="S7" t="n">
-        <v>6.592129512259694</v>
+        <v>0.001390615588901937</v>
       </c>
       <c r="T7" t="n">
-        <v>-807.1496285400052</v>
+        <v>-0.8913034347668554</v>
       </c>
       <c r="U7" t="n">
-        <v>559.3642401743447</v>
+        <v>0.1926362571453079</v>
       </c>
       <c r="V7" t="n">
-        <v>671.4209508671074</v>
+        <v>0.1238414569456767</v>
       </c>
       <c r="W7" t="n">
-        <v>-325.900343260118</v>
+        <v>-0.1046174260773613</v>
       </c>
       <c r="X7" t="n">
-        <v>-62.96204323074618</v>
+        <v>-0.0297927128580371</v>
       </c>
       <c r="Y7" t="n">
-        <v>-1819.856545372002</v>
+        <v>-1</v>
       </c>
       <c r="Z7" t="n">
-        <v>-1106.502485799102</v>
+        <v>-0.4782998751406419</v>
       </c>
     </row>
     <row r="8">
@@ -959,79 +959,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-1625.648774815199</v>
+        <v>-0.03676971840287516</v>
       </c>
       <c r="C8" t="n">
-        <v>157.3227343992426</v>
+        <v>0.002177388460173155</v>
       </c>
       <c r="D8" t="n">
-        <v>-81.29808902396032</v>
+        <v>-0.003410242326084702</v>
       </c>
       <c r="E8" t="n">
-        <v>668.9434063525875</v>
+        <v>0.02236355064509105</v>
       </c>
       <c r="F8" t="n">
-        <v>-741.9441609491929</v>
+        <v>-0.0163653868091824</v>
       </c>
       <c r="G8" t="n">
-        <v>-2100.522153675745</v>
+        <v>-0.02290069796291095</v>
       </c>
       <c r="H8" t="n">
-        <v>188.5157617131201</v>
+        <v>0.004812283996332891</v>
       </c>
       <c r="I8" t="n">
-        <v>-812.7385425176176</v>
+        <v>-0.01501047380695588</v>
       </c>
       <c r="J8" t="n">
-        <v>-1907.975664674643</v>
+        <v>-0.01774563203302675</v>
       </c>
       <c r="K8" t="n">
-        <v>1626.723159813758</v>
+        <v>0.05550132784342088</v>
       </c>
       <c r="L8" t="n">
-        <v>-192.1666819984046</v>
+        <v>-0.02651788200403524</v>
       </c>
       <c r="M8" t="n">
-        <v>-2341.149250483978</v>
+        <v>-0.01943168108387035</v>
       </c>
       <c r="N8" t="n">
-        <v>1694.798905015578</v>
+        <v>0.01706599372678591</v>
       </c>
       <c r="O8" t="n">
-        <v>-2904.548264572672</v>
+        <v>-0.04523533323876584</v>
       </c>
       <c r="P8" t="n">
-        <v>-447.8200000506046</v>
+        <v>-0.007075462288094624</v>
       </c>
       <c r="Q8" t="n">
-        <v>3995.749324793615</v>
+        <v>0.463707693239981</v>
       </c>
       <c r="R8" t="n">
-        <v>2504.951216050418</v>
+        <v>0.1867597817081045</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6211574438853223</v>
+        <v>-0.000131033715739804</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.01155440199519992</v>
+        <v>-1.275906947219548e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0.002237638191461845</v>
+        <v>7.706074416095216e-07</v>
       </c>
       <c r="V8" t="n">
-        <v>0.003923415114721504</v>
+        <v>7.236614278751775e-07</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0007033726939772153</v>
+        <v>2.257900070950946e-07</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0006764296591038954</v>
+        <v>-3.200765662652629e-07</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0006169683334045177</v>
+        <v>3.390203117786965e-07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.001463586448787388</v>
+        <v>6.326539928258619e-07</v>
       </c>
     </row>
     <row r="9">
@@ -1041,79 +1041,79 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1767.016120972824</v>
+        <v>-0.03996723412097272</v>
       </c>
       <c r="C9" t="n">
-        <v>1329.681228591683</v>
+        <v>0.01840314163048472</v>
       </c>
       <c r="D9" t="n">
-        <v>830.8806168855929</v>
+        <v>0.0348532700048032</v>
       </c>
       <c r="E9" t="n">
-        <v>118.920238445816</v>
+        <v>0.003975640913646361</v>
       </c>
       <c r="F9" t="n">
-        <v>-118.0194382085259</v>
+        <v>-0.002603206358297884</v>
       </c>
       <c r="G9" t="n">
-        <v>-450.4904970805362</v>
+        <v>-0.00491142013939241</v>
       </c>
       <c r="H9" t="n">
-        <v>-2790.268737721351</v>
+        <v>-0.07122781389727116</v>
       </c>
       <c r="I9" t="n">
-        <v>2354.863304218457</v>
+        <v>0.0434919867801969</v>
       </c>
       <c r="J9" t="n">
-        <v>5655.098125476743</v>
+        <v>0.05259673501259375</v>
       </c>
       <c r="K9" t="n">
-        <v>-531.213035768031</v>
+        <v>-0.01812418337748129</v>
       </c>
       <c r="L9" t="n">
-        <v>1181.952907283581</v>
+        <v>0.1631026117729014</v>
       </c>
       <c r="M9" t="n">
-        <v>2822.332478128236</v>
+        <v>0.02342553112164888</v>
       </c>
       <c r="N9" t="n">
-        <v>3096.7009691879</v>
+        <v>0.03118262535896953</v>
       </c>
       <c r="O9" t="n">
-        <v>-1988.401727148811</v>
+        <v>-0.03096729905892861</v>
       </c>
       <c r="P9" t="n">
-        <v>-3613.765689317985</v>
+        <v>-0.05709674165935046</v>
       </c>
       <c r="Q9" t="n">
-        <v>1001.717043175706</v>
+        <v>0.1162495095695657</v>
       </c>
       <c r="R9" t="n">
-        <v>62.38414312211581</v>
+        <v>0.004651128084603384</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6014093097231288</v>
+        <v>0.0001268678292585689</v>
       </c>
       <c r="T9" t="n">
-        <v>0.01223535867262815</v>
+        <v>1.351102301842587e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0004042835831411558</v>
+        <v>-1.392289150578026e-07</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.0002716423968199723</v>
+        <v>-5.01035753307308e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0005968932298803008</v>
+        <v>-1.91608983066455e-07</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0004304525110634277</v>
+        <v>2.036837974608683e-07</v>
       </c>
       <c r="Y9" t="n">
-        <v>-8.994694490278034e-05</v>
+        <v>-4.942529406041399e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>-6.830756442500896e-05</v>
+        <v>-2.952681982639037e-08</v>
       </c>
     </row>
     <row r="10">
@@ -1123,79 +1123,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-42.33092912333313</v>
+        <v>-0.0009574616409832843</v>
       </c>
       <c r="C10" t="n">
-        <v>-35.17885956575779</v>
+        <v>-0.0004868847668649584</v>
       </c>
       <c r="D10" t="n">
-        <v>15.85257659340057</v>
+        <v>0.0006649741503810902</v>
       </c>
       <c r="E10" t="n">
-        <v>15.97664013565432</v>
+        <v>0.0005341175313473027</v>
       </c>
       <c r="F10" t="n">
-        <v>-8.749752556294698</v>
+        <v>-0.0001929971183885372</v>
       </c>
       <c r="G10" t="n">
-        <v>23.82517012712892</v>
+        <v>0.0002597511404683683</v>
       </c>
       <c r="H10" t="n">
-        <v>2.599949852325851</v>
+        <v>6.636950115956793e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>-22.48624060971693</v>
+        <v>-0.0004152985345613125</v>
       </c>
       <c r="J10" t="n">
-        <v>14.92572749097707</v>
+        <v>0.0001388206740704301</v>
       </c>
       <c r="K10" t="n">
-        <v>21.18274376762598</v>
+        <v>0.0007227231009637751</v>
       </c>
       <c r="L10" t="n">
-        <v>47.63748537968184</v>
+        <v>0.006573695310396443</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.936306460150833</v>
+        <v>-7.417188680537296e-05</v>
       </c>
       <c r="N10" t="n">
-        <v>11.8797216050736</v>
+        <v>0.0001196243718285183</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.486520510411297</v>
+        <v>-0.0001010208439045215</v>
       </c>
       <c r="P10" t="n">
-        <v>29.29656846513011</v>
+        <v>0.0004628796510253818</v>
       </c>
       <c r="Q10" t="n">
-        <v>-21.00907006522307</v>
+        <v>-0.002438107755311932</v>
       </c>
       <c r="R10" t="n">
-        <v>-3.015431143552671</v>
+        <v>-0.0002248192533719913</v>
       </c>
       <c r="S10" t="n">
-        <v>-11.31076407582609</v>
+        <v>-0.002386015750598339</v>
       </c>
       <c r="T10" t="n">
-        <v>1.724346469887739</v>
+        <v>0.001904127657370121</v>
       </c>
       <c r="U10" t="n">
-        <v>26.47026756011147</v>
+        <v>0.00911594432069061</v>
       </c>
       <c r="V10" t="n">
-        <v>-47.13963597941531</v>
+        <v>-0.008694755789256122</v>
       </c>
       <c r="W10" t="n">
-        <v>160.4336858144833</v>
+        <v>0.05150089471559411</v>
       </c>
       <c r="X10" t="n">
-        <v>32.30871624199563</v>
+        <v>0.01528800935322136</v>
       </c>
       <c r="Y10" t="n">
-        <v>-23.99679652286095</v>
+        <v>-0.01318609237848234</v>
       </c>
       <c r="Z10" t="n">
-        <v>-17.78328851825467</v>
+        <v>-0.007687054287752893</v>
       </c>
     </row>
     <row r="11">
@@ -1205,79 +1205,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-16783.31084452912</v>
+        <v>-0.3796131262679476</v>
       </c>
       <c r="C11" t="n">
-        <v>401.1252714444851</v>
+        <v>0.00555168037513624</v>
       </c>
       <c r="D11" t="n">
-        <v>-4740.212669807703</v>
+        <v>-0.1988395308585536</v>
       </c>
       <c r="E11" t="n">
-        <v>-14614.27267891501</v>
+        <v>-0.4885720138540716</v>
       </c>
       <c r="F11" t="n">
-        <v>22113.49335675132</v>
+        <v>0.4877669931690491</v>
       </c>
       <c r="G11" t="n">
-        <v>-7432.280111702724</v>
+        <v>-0.08102956767964102</v>
       </c>
       <c r="H11" t="n">
-        <v>39173.86460499317</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>7542.279764983296</v>
+        <v>0.1392984175529746</v>
       </c>
       <c r="J11" t="n">
-        <v>14182.44338363622</v>
+        <v>0.1319075637467107</v>
       </c>
       <c r="K11" t="n">
-        <v>204.2540422541997</v>
+        <v>0.006968838240301544</v>
       </c>
       <c r="L11" t="n">
-        <v>-7246.682897569365</v>
+        <v>-1</v>
       </c>
       <c r="M11" t="n">
-        <v>19891.43448370156</v>
+        <v>0.1651001152993921</v>
       </c>
       <c r="N11" t="n">
-        <v>-27050.75373168485</v>
+        <v>-0.2723910147236737</v>
       </c>
       <c r="O11" t="n">
-        <v>-37007.45889407125</v>
+        <v>-0.5763528724283512</v>
       </c>
       <c r="P11" t="n">
-        <v>13540.12725072249</v>
+        <v>0.2139311770971895</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2450.978362660263</v>
+        <v>-0.2844366426287264</v>
       </c>
       <c r="R11" t="n">
-        <v>3074.154573216961</v>
+        <v>0.2291974523704318</v>
       </c>
       <c r="S11" t="n">
-        <v>3.162272035945706</v>
+        <v>0.00066708410102631</v>
       </c>
       <c r="T11" t="n">
-        <v>0.10542248318573</v>
+        <v>0.0001164138816926124</v>
       </c>
       <c r="U11" t="n">
-        <v>0.002323957233121941</v>
+        <v>8.003343635532412e-07</v>
       </c>
       <c r="V11" t="n">
-        <v>0.008927662416398356</v>
+        <v>1.646678911848201e-06</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.004581866323544828</v>
+        <v>-1.470827114217593e-06</v>
       </c>
       <c r="X11" t="n">
-        <v>0.002419146308776754</v>
+        <v>1.144704454314324e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0005714210518001463</v>
+        <v>3.139923601414091e-07</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.003808913711840942</v>
+        <v>1.646451748799569e-06</v>
       </c>
     </row>
     <row r="12">
@@ -1287,79 +1287,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>777.5789603823658</v>
+        <v>0.01758766090941767</v>
       </c>
       <c r="C12" t="n">
-        <v>-466.7241335776929</v>
+        <v>-0.006459586063114315</v>
       </c>
       <c r="D12" t="n">
-        <v>617.9216075570894</v>
+        <v>0.0259201962259215</v>
       </c>
       <c r="E12" t="n">
-        <v>1696.195430514218</v>
+        <v>0.05670577219843763</v>
       </c>
       <c r="F12" t="n">
-        <v>2843.792971170505</v>
+        <v>0.0627267851517284</v>
       </c>
       <c r="G12" t="n">
-        <v>-267.0770257023835</v>
+        <v>-0.002911776144679047</v>
       </c>
       <c r="H12" t="n">
-        <v>887.6995959879391</v>
+        <v>0.02266050605267042</v>
       </c>
       <c r="I12" t="n">
-        <v>192.0844504691421</v>
+        <v>0.003547609054640189</v>
       </c>
       <c r="J12" t="n">
-        <v>627.7855757410662</v>
+        <v>0.00583888569912265</v>
       </c>
       <c r="K12" t="n">
-        <v>-351.9282231473332</v>
+        <v>-0.01200725739497615</v>
       </c>
       <c r="L12" t="n">
-        <v>341.2461406890916</v>
+        <v>0.04708997834078681</v>
       </c>
       <c r="M12" t="n">
-        <v>-586.6445663442425</v>
+        <v>-0.00486918555937011</v>
       </c>
       <c r="N12" t="n">
-        <v>750.4497547203354</v>
+        <v>0.007556749516667614</v>
       </c>
       <c r="O12" t="n">
-        <v>948.4808968544545</v>
+        <v>0.01477160836441706</v>
       </c>
       <c r="P12" t="n">
-        <v>-6.030966700024721</v>
+        <v>-9.528801179482246e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>534.0805041246791</v>
+        <v>0.0619801740402954</v>
       </c>
       <c r="R12" t="n">
-        <v>638.5411622149019</v>
+        <v>0.04760723773891418</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4053422406437445</v>
+        <v>-8.550730649805015e-05</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.006571862694740241</v>
+        <v>-7.25704824176577e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0004500036782029246</v>
+        <v>1.549741975704669e-07</v>
       </c>
       <c r="V12" t="n">
-        <v>0.0005973512776355915</v>
+        <v>1.101795415159678e-07</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0003431536909194559</v>
+        <v>1.101559315151943e-07</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.0002833750392481139</v>
+        <v>-1.340889009035738e-07</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0001020259631728847</v>
+        <v>5.606264044951371e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0002131103340158913</v>
+        <v>9.211967208312986e-08</v>
       </c>
     </row>
     <row r="13">
@@ -1369,79 +1369,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>204.4522441814625</v>
+        <v>0.004624400769620634</v>
       </c>
       <c r="C13" t="n">
-        <v>-61.80044789584773</v>
+        <v>-0.0008553346253216343</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4936938283903399</v>
+        <v>-2.070916561405688e-05</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.909977505163881</v>
+        <v>-0.0001641462185892514</v>
       </c>
       <c r="F13" t="n">
-        <v>-272.3997588880969</v>
+        <v>-0.006008440601821787</v>
       </c>
       <c r="G13" t="n">
-        <v>306.0540653478751</v>
+        <v>0.00333671877660884</v>
       </c>
       <c r="H13" t="n">
-        <v>241.1668823284105</v>
+        <v>0.006156320923661715</v>
       </c>
       <c r="I13" t="n">
-        <v>179.1856168667506</v>
+        <v>0.003309380406926237</v>
       </c>
       <c r="J13" t="n">
-        <v>158.532032232844</v>
+        <v>0.001474469072922748</v>
       </c>
       <c r="K13" t="n">
-        <v>-520.4691251396202</v>
+        <v>-0.01775761743630657</v>
       </c>
       <c r="L13" t="n">
-        <v>40.08497156524274</v>
+        <v>0.005531492426512519</v>
       </c>
       <c r="M13" t="n">
-        <v>-357.5804526955663</v>
+        <v>-0.002967939492610228</v>
       </c>
       <c r="N13" t="n">
-        <v>126.6006057542539</v>
+        <v>0.001274820946140235</v>
       </c>
       <c r="O13" t="n">
-        <v>-229.7656369779475</v>
+        <v>-0.003578362006335567</v>
       </c>
       <c r="P13" t="n">
-        <v>98.82964936446545</v>
+        <v>0.001561487778448644</v>
       </c>
       <c r="Q13" t="n">
-        <v>98.68146404984539</v>
+        <v>0.01145200820686153</v>
       </c>
       <c r="R13" t="n">
-        <v>-10.38681320939595</v>
+        <v>-0.000774401894615819</v>
       </c>
       <c r="S13" t="n">
-        <v>0.02258653930194275</v>
+        <v>4.764650572203521e-06</v>
       </c>
       <c r="T13" t="n">
-        <v>0.000154555994032929</v>
+        <v>1.706700758749436e-07</v>
       </c>
       <c r="U13" t="n">
-        <v>1.126989292251032e-05</v>
+        <v>3.881174081389474e-09</v>
       </c>
       <c r="V13" t="n">
-        <v>3.067720143458954e-05</v>
+        <v>5.658312144965401e-09</v>
       </c>
       <c r="W13" t="n">
-        <v>-7.336431215317105e-06</v>
+        <v>-2.355071316164546e-09</v>
       </c>
       <c r="X13" t="n">
-        <v>6.786984313967228e-06</v>
+        <v>3.211501159468189e-09</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.221052654367301e-06</v>
+        <v>3.418430243959497e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.130829922379446e-05</v>
+        <v>4.888157212667963e-09</v>
       </c>
     </row>
     <row r="14">
@@ -1451,79 +1451,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-261.0930915254704</v>
+        <v>-0.005905531133820099</v>
       </c>
       <c r="C14" t="n">
-        <v>188.4874930056041</v>
+        <v>0.002608717002819564</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.13869611585458</v>
+        <v>-0.000676976116448266</v>
       </c>
       <c r="E14" t="n">
-        <v>-232.192602876519</v>
+        <v>-0.007762466876170383</v>
       </c>
       <c r="F14" t="n">
-        <v>321.2650236302609</v>
+        <v>0.007086283114950452</v>
       </c>
       <c r="G14" t="n">
-        <v>603.9994916760037</v>
+        <v>0.006585034061373262</v>
       </c>
       <c r="H14" t="n">
-        <v>-138.8027602178944</v>
+        <v>-0.003543249092666808</v>
       </c>
       <c r="I14" t="n">
-        <v>-356.7405908872147</v>
+        <v>-0.006588644459758007</v>
       </c>
       <c r="J14" t="n">
-        <v>63.32174914629695</v>
+        <v>0.0005889406667193669</v>
       </c>
       <c r="K14" t="n">
-        <v>-66.96305361076244</v>
+        <v>-0.002284677862625991</v>
       </c>
       <c r="L14" t="n">
-        <v>163.2985856486096</v>
+        <v>0.02253425297571419</v>
       </c>
       <c r="M14" t="n">
-        <v>-343.5552590762249</v>
+        <v>-0.002851529533059706</v>
       </c>
       <c r="N14" t="n">
-        <v>-563.5432845612887</v>
+        <v>-0.00567467097756172</v>
       </c>
       <c r="O14" t="n">
-        <v>60.04235031333381</v>
+        <v>0.0009350974669591058</v>
       </c>
       <c r="P14" t="n">
-        <v>-561.4504852439011</v>
+        <v>-0.008870800175353371</v>
       </c>
       <c r="Q14" t="n">
-        <v>308.7035363339419</v>
+        <v>0.03582512142095665</v>
       </c>
       <c r="R14" t="n">
-        <v>17.80002946435926</v>
+        <v>0.001327103536332763</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01757339615947921</v>
+        <v>3.707123563618254e-06</v>
       </c>
       <c r="T14" t="n">
-        <v>0.001262512372909537</v>
+        <v>1.394142516605458e-06</v>
       </c>
       <c r="U14" t="n">
-        <v>-6.018742062970493e-05</v>
+        <v>-2.072760216799505e-08</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.95998638520962e-05</v>
+        <v>-1.283747331913439e-08</v>
       </c>
       <c r="W14" t="n">
-        <v>-5.998293028502612e-05</v>
+        <v>-1.925514932639586e-08</v>
       </c>
       <c r="X14" t="n">
-        <v>3.624892347528249e-05</v>
+        <v>1.715245746638475e-08</v>
       </c>
       <c r="Y14" t="n">
-        <v>-2.232439101568113e-05</v>
+        <v>-1.226711581880084e-08</v>
       </c>
       <c r="Z14" t="n">
-        <v>-2.047373345616134e-05</v>
+        <v>-8.850033580062567e-09</v>
       </c>
     </row>
     <row r="15">
@@ -1533,79 +1533,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>800.5539832000063</v>
+        <v>0.01810732120282903</v>
       </c>
       <c r="C15" t="n">
-        <v>-610.9204287084967</v>
+        <v>-0.008455301114829348</v>
       </c>
       <c r="D15" t="n">
-        <v>384.7884093928076</v>
+        <v>0.01614086795953371</v>
       </c>
       <c r="E15" t="n">
-        <v>1433.082675505869</v>
+        <v>0.04790960892644742</v>
       </c>
       <c r="F15" t="n">
-        <v>-638.7657498278148</v>
+        <v>-0.01408953547530577</v>
       </c>
       <c r="G15" t="n">
-        <v>-373.2295803001149</v>
+        <v>-0.004069091999015581</v>
       </c>
       <c r="H15" t="n">
-        <v>-223.9284475551311</v>
+        <v>-0.005716271545151274</v>
       </c>
       <c r="I15" t="n">
-        <v>-2078.965304508203</v>
+        <v>-0.03839642470039985</v>
       </c>
       <c r="J15" t="n">
-        <v>999.1338770927358</v>
+        <v>0.00929270873988978</v>
       </c>
       <c r="K15" t="n">
-        <v>-155.3392673302704</v>
+        <v>-0.005299940282427162</v>
       </c>
       <c r="L15" t="n">
-        <v>-771.8068811702485</v>
+        <v>-0.106504850851018</v>
       </c>
       <c r="M15" t="n">
-        <v>208.423609287977</v>
+        <v>0.001729928625949806</v>
       </c>
       <c r="N15" t="n">
-        <v>-733.1029754666725</v>
+        <v>-0.007382073910584291</v>
       </c>
       <c r="O15" t="n">
-        <v>-872.4922302731128</v>
+        <v>-0.01358816352478305</v>
       </c>
       <c r="P15" t="n">
-        <v>-343.7553565053988</v>
+        <v>-0.00543126269708728</v>
       </c>
       <c r="Q15" t="n">
-        <v>-353.0642519416034</v>
+        <v>-0.04097319339265524</v>
       </c>
       <c r="R15" t="n">
-        <v>11.97835907038351</v>
+        <v>0.0008930615937237043</v>
       </c>
       <c r="S15" t="n">
-        <v>2341.263824446673</v>
+        <v>0.4938916879519359</v>
       </c>
       <c r="T15" t="n">
-        <v>53.05811038065642</v>
+        <v>0.05858997433977522</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.783966488315329</v>
+        <v>-0.0006143700338702585</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.268903658126448</v>
+        <v>-0.0002340452402373442</v>
       </c>
       <c r="W15" t="n">
-        <v>-2.572851359455732</v>
+        <v>-0.0008259122534616788</v>
       </c>
       <c r="X15" t="n">
-        <v>1.806775200426608</v>
+        <v>0.0008549394521403693</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0.4449129445343895</v>
+        <v>-0.0002444769318031293</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.3165671640966038</v>
+        <v>-0.0001368402122944021</v>
       </c>
     </row>
     <row r="16">
@@ -1615,79 +1615,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-590.981278621824</v>
+        <v>-0.0133671033577138</v>
       </c>
       <c r="C16" t="n">
-        <v>373.4534751160041</v>
+        <v>0.005168695358838515</v>
       </c>
       <c r="D16" t="n">
-        <v>192.5250049335187</v>
+        <v>0.008075920707809624</v>
       </c>
       <c r="E16" t="n">
-        <v>-174.7143396273532</v>
+        <v>-0.005840902153418522</v>
       </c>
       <c r="F16" t="n">
-        <v>335.7530103104184</v>
+        <v>0.007405850972730649</v>
       </c>
       <c r="G16" t="n">
-        <v>380.5141633857958</v>
+        <v>0.004148511317083224</v>
       </c>
       <c r="H16" t="n">
-        <v>-684.4758947168191</v>
+        <v>-0.01747276919493857</v>
       </c>
       <c r="I16" t="n">
-        <v>-484.7628446156234</v>
+        <v>-0.008953088356247734</v>
       </c>
       <c r="J16" t="n">
-        <v>150.3842332067109</v>
+        <v>0.001398688314250721</v>
       </c>
       <c r="K16" t="n">
-        <v>-677.1346260329776</v>
+        <v>-0.02310280679712656</v>
       </c>
       <c r="L16" t="n">
-        <v>-944.0375720394566</v>
+        <v>-0.1302716822832277</v>
       </c>
       <c r="M16" t="n">
-        <v>329.5398911466492</v>
+        <v>0.002735201127331485</v>
       </c>
       <c r="N16" t="n">
-        <v>299.1926426307112</v>
+        <v>0.003012758473660499</v>
       </c>
       <c r="O16" t="n">
-        <v>229.1831704979779</v>
+        <v>0.003569290693717626</v>
       </c>
       <c r="P16" t="n">
-        <v>1177.314735637487</v>
+        <v>0.01860132645321741</v>
       </c>
       <c r="Q16" t="n">
-        <v>507.9105217080811</v>
+        <v>0.05894314113554521</v>
       </c>
       <c r="R16" t="n">
-        <v>212.1243354704897</v>
+        <v>0.015815196053961</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.541570700205408</v>
+        <v>-0.001168999272295286</v>
       </c>
       <c r="T16" t="n">
-        <v>641.2803456546077</v>
+        <v>0.708140541134002</v>
       </c>
       <c r="U16" t="n">
-        <v>-444.4173842993641</v>
+        <v>-0.1530503657063489</v>
       </c>
       <c r="V16" t="n">
-        <v>-533.4467892363238</v>
+        <v>-0.09839256206810755</v>
       </c>
       <c r="W16" t="n">
-        <v>258.9297734821585</v>
+        <v>0.08311917123351059</v>
       </c>
       <c r="X16" t="n">
-        <v>50.02345914499693</v>
+        <v>0.02367036515970102</v>
       </c>
       <c r="Y16" t="n">
-        <v>1445.885697623696</v>
+        <v>0.7945053148835632</v>
       </c>
       <c r="Z16" t="n">
-        <v>879.1222967665814</v>
+        <v>0.3800118754122293</v>
       </c>
     </row>
     <row r="17">
@@ -1697,79 +1697,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-169.1535307607658</v>
+        <v>-0.00382599721986841</v>
       </c>
       <c r="C17" t="n">
-        <v>-105.2131844357733</v>
+        <v>-0.001456178438058126</v>
       </c>
       <c r="D17" t="n">
-        <v>-11.9008173625927</v>
+        <v>-0.0004992081803172046</v>
       </c>
       <c r="E17" t="n">
-        <v>-34.09875941581196</v>
+        <v>-0.001139960908334822</v>
       </c>
       <c r="F17" t="n">
-        <v>-84.45985076776657</v>
+        <v>-0.001862967862557211</v>
       </c>
       <c r="G17" t="n">
-        <v>-47.20669173705444</v>
+        <v>-0.0005146654546855164</v>
       </c>
       <c r="H17" t="n">
-        <v>203.9277079254716</v>
+        <v>0.005205708192994535</v>
       </c>
       <c r="I17" t="n">
-        <v>2.73138231375721</v>
+        <v>5.044591899189573e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>28.27872517544458</v>
+        <v>0.0002630137588322452</v>
       </c>
       <c r="K17" t="n">
-        <v>-55.47401635610668</v>
+        <v>-0.001892689330693532</v>
       </c>
       <c r="L17" t="n">
-        <v>-265.153330006014</v>
+        <v>-0.03658961400048979</v>
       </c>
       <c r="M17" t="n">
-        <v>-6.906491818880126</v>
+        <v>-5.73243019021938e-05</v>
       </c>
       <c r="N17" t="n">
-        <v>67.83601950610228</v>
+        <v>0.000683083450145743</v>
       </c>
       <c r="O17" t="n">
-        <v>201.5717751808799</v>
+        <v>0.003139271787304313</v>
       </c>
       <c r="P17" t="n">
-        <v>-195.6384614646207</v>
+        <v>-0.003091046751010129</v>
       </c>
       <c r="Q17" t="n">
-        <v>14.30318186974347</v>
+        <v>0.001659887778659198</v>
       </c>
       <c r="R17" t="n">
-        <v>-12.69887971027372</v>
+        <v>-0.0009467809143076193</v>
       </c>
       <c r="S17" t="n">
-        <v>18.68504172241123</v>
+        <v>0.003941626184701777</v>
       </c>
       <c r="T17" t="n">
-        <v>-316.8160981027178</v>
+        <v>-0.3498474959830693</v>
       </c>
       <c r="U17" t="n">
-        <v>-141.5402775743308</v>
+        <v>-0.04874424811054911</v>
       </c>
       <c r="V17" t="n">
-        <v>-225.2535571780295</v>
+        <v>-0.04154730153579135</v>
       </c>
       <c r="W17" t="n">
-        <v>-10.3752898804874</v>
+        <v>-0.003330576799168151</v>
       </c>
       <c r="X17" t="n">
-        <v>190.6795300847751</v>
+        <v>0.09022674926386479</v>
       </c>
       <c r="Y17" t="n">
-        <v>-169.3478596088431</v>
+        <v>-0.09305560926739211</v>
       </c>
       <c r="Z17" t="n">
-        <v>284.954918606762</v>
+        <v>0.1231754141897805</v>
       </c>
     </row>
     <row r="18">
@@ -1779,79 +1779,79 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-1327.789286242476</v>
+        <v>-0.03003258693381693</v>
       </c>
       <c r="C18" t="n">
-        <v>814.5044945511592</v>
+        <v>0.01127295869835454</v>
       </c>
       <c r="D18" t="n">
-        <v>-7016.705818461509</v>
+        <v>-0.2943324678240584</v>
       </c>
       <c r="E18" t="n">
-        <v>3394.559403012889</v>
+        <v>0.1134840412598905</v>
       </c>
       <c r="F18" t="n">
-        <v>66.76390755566145</v>
+        <v>0.001472640704717017</v>
       </c>
       <c r="G18" t="n">
-        <v>897.1466952013991</v>
+        <v>0.009781037281267597</v>
       </c>
       <c r="H18" t="n">
-        <v>-214.7806288497054</v>
+        <v>-0.005482753131850286</v>
       </c>
       <c r="I18" t="n">
-        <v>234.8107913737272</v>
+        <v>0.00433672214263114</v>
       </c>
       <c r="J18" t="n">
-        <v>307.4560317863815</v>
+        <v>0.002859576098076746</v>
       </c>
       <c r="K18" t="n">
-        <v>-238.2816241331954</v>
+        <v>-0.008129807742820466</v>
       </c>
       <c r="L18" t="n">
-        <v>26.80495523885323</v>
+        <v>0.003698927580761671</v>
       </c>
       <c r="M18" t="n">
-        <v>193.0037789587512</v>
+        <v>0.001601943096935385</v>
       </c>
       <c r="N18" t="n">
-        <v>108.5727898380239</v>
+        <v>0.001093287554524547</v>
       </c>
       <c r="O18" t="n">
-        <v>106.9755043244865</v>
+        <v>0.001666032768512155</v>
       </c>
       <c r="P18" t="n">
-        <v>271.3459212234685</v>
+        <v>0.004287208772337086</v>
       </c>
       <c r="Q18" t="n">
-        <v>-327.8064096334494</v>
+        <v>-0.03804201457213745</v>
       </c>
       <c r="R18" t="n">
-        <v>10.68295448409671</v>
+        <v>0.0007964810790180917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.007204935159865707</v>
+        <v>-1.519887485781881e-06</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0002594416654502667</v>
+        <v>2.864911775475034e-07</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.950833479007668e-05</v>
+        <v>-1.36060498569447e-08</v>
       </c>
       <c r="V18" t="n">
-        <v>-6.924957253217904e-05</v>
+        <v>-1.277286320031408e-08</v>
       </c>
       <c r="W18" t="n">
-        <v>-1.359728613247017e-05</v>
+        <v>-4.364871367076306e-09</v>
       </c>
       <c r="X18" t="n">
-        <v>8.596497309047079e-06</v>
+        <v>4.067736095773031e-09</v>
       </c>
       <c r="Y18" t="n">
-        <v>-1.43661718632036e-05</v>
+        <v>-7.894123248196452e-09</v>
       </c>
       <c r="Z18" t="n">
-        <v>-2.453562229805568e-05</v>
+        <v>-1.060583706974941e-08</v>
       </c>
     </row>
     <row r="19">
@@ -1861,79 +1861,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-272.9300668428349</v>
+        <v>-0.006173265625983546</v>
       </c>
       <c r="C19" t="n">
-        <v>-194.7725258771987</v>
+        <v>-0.002695703528312379</v>
       </c>
       <c r="D19" t="n">
-        <v>26.74103906322611</v>
+        <v>0.001121716689183449</v>
       </c>
       <c r="E19" t="n">
-        <v>4.666413242686819</v>
+        <v>0.0001560035839993694</v>
       </c>
       <c r="F19" t="n">
-        <v>-104.808955469662</v>
+        <v>-0.002311816963601456</v>
       </c>
       <c r="G19" t="n">
-        <v>14.75014558032767</v>
+        <v>0.0001608117430482448</v>
       </c>
       <c r="H19" t="n">
-        <v>210.8576681628694</v>
+        <v>0.005382610837328343</v>
       </c>
       <c r="I19" t="n">
-        <v>-54.75700704746084</v>
+        <v>-0.00101130754484354</v>
       </c>
       <c r="J19" t="n">
-        <v>62.07245067328485</v>
+        <v>0.0005773212360253829</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.762004053446777</v>
+        <v>-0.0001283538745108496</v>
       </c>
       <c r="L19" t="n">
-        <v>-146.8714474602496</v>
+        <v>-0.02026740365712873</v>
       </c>
       <c r="M19" t="n">
-        <v>-25.43234679950352</v>
+        <v>-0.0002110900243203975</v>
       </c>
       <c r="N19" t="n">
-        <v>100.3596384950647</v>
+        <v>0.001010584179580605</v>
       </c>
       <c r="O19" t="n">
-        <v>183.5096194927269</v>
+        <v>0.002857972405390177</v>
       </c>
       <c r="P19" t="n">
-        <v>-124.8113858420907</v>
+        <v>-0.001971993777747193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-37.74232423186292</v>
+        <v>-0.004380006022519082</v>
       </c>
       <c r="R19" t="n">
-        <v>-20.12416190302152</v>
+        <v>-0.001500382147159231</v>
       </c>
       <c r="S19" t="n">
-        <v>-16.59984177107744</v>
+        <v>-0.003501751398730173</v>
       </c>
       <c r="T19" t="n">
-        <v>36.36933142219372</v>
+        <v>0.04016121530701879</v>
       </c>
       <c r="U19" t="n">
-        <v>-581.4697053492829</v>
+        <v>-0.2002490320921454</v>
       </c>
       <c r="V19" t="n">
-        <v>330.0600283881298</v>
+        <v>0.06087852150328222</v>
       </c>
       <c r="W19" t="n">
-        <v>265.1379395199959</v>
+        <v>0.085112057601909</v>
       </c>
       <c r="X19" t="n">
-        <v>-855.9181058058849</v>
+        <v>-0.4050078594624976</v>
       </c>
       <c r="Y19" t="n">
-        <v>26.88475679233423</v>
+        <v>0.01477300881803222</v>
       </c>
       <c r="Z19" t="n">
-        <v>-181.8367728146449</v>
+        <v>-0.07860127460121477</v>
       </c>
     </row>
     <row r="20">
@@ -1943,79 +1943,79 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-252.3703357913425</v>
+        <v>-0.005708235582031916</v>
       </c>
       <c r="C20" t="n">
-        <v>-177.3526941800069</v>
+        <v>-0.002454608427464663</v>
       </c>
       <c r="D20" t="n">
-        <v>19.06391949646523</v>
+        <v>0.0007996815909013119</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.052740432763812</v>
+        <v>-0.0001020566383136554</v>
       </c>
       <c r="F20" t="n">
-        <v>-100.6702462821001</v>
+        <v>-0.002220527645199764</v>
       </c>
       <c r="G20" t="n">
-        <v>2.82153232473383</v>
+        <v>3.076142731855897e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>209.5393928270437</v>
+        <v>0.005348958928099615</v>
       </c>
       <c r="I20" t="n">
-        <v>-43.59803872163651</v>
+        <v>-0.0008052124810502474</v>
       </c>
       <c r="J20" t="n">
-        <v>55.10391777395249</v>
+        <v>0.0005125085536987034</v>
       </c>
       <c r="K20" t="n">
-        <v>-14.02811372008277</v>
+        <v>-0.0004786179712915891</v>
       </c>
       <c r="L20" t="n">
-        <v>-170.1593301011369</v>
+        <v>-0.02348099571987767</v>
       </c>
       <c r="M20" t="n">
-        <v>-21.43250994734529</v>
+        <v>-0.0001778911353206538</v>
       </c>
       <c r="N20" t="n">
-        <v>94.24918701493068</v>
+        <v>0.0009490542090813394</v>
       </c>
       <c r="O20" t="n">
-        <v>186.8767462591354</v>
+        <v>0.0029104119200622</v>
       </c>
       <c r="P20" t="n">
-        <v>-138.940836588866</v>
+        <v>-0.002195236142757694</v>
       </c>
       <c r="Q20" t="n">
-        <v>-27.48408141830062</v>
+        <v>-0.00318953441754214</v>
       </c>
       <c r="R20" t="n">
-        <v>-18.66023262084158</v>
+        <v>-0.001391237062247316</v>
       </c>
       <c r="S20" t="n">
-        <v>-31.47934652280163</v>
+        <v>-0.006640596171789746</v>
       </c>
       <c r="T20" t="n">
-        <v>905.5834377561185</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>190.2512436502434</v>
+        <v>0.06551953961626135</v>
       </c>
       <c r="V20" t="n">
-        <v>187.997535519738</v>
+        <v>0.03467554694397535</v>
       </c>
       <c r="W20" t="n">
-        <v>-120.1881278324109</v>
+        <v>-0.03858164877368025</v>
       </c>
       <c r="X20" t="n">
-        <v>207.1683327618618</v>
+        <v>0.09802900818565576</v>
       </c>
       <c r="Y20" t="n">
-        <v>-320.5259182488563</v>
+        <v>-0.1761270244426528</v>
       </c>
       <c r="Z20" t="n">
-        <v>108.219978596485</v>
+        <v>0.04677947217898943</v>
       </c>
     </row>
     <row r="21">
@@ -2025,79 +2025,79 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-51.99469070905948</v>
+        <v>-0.001176041322969065</v>
       </c>
       <c r="C21" t="n">
-        <v>-47.21471002724537</v>
+        <v>-0.0006534641363584177</v>
       </c>
       <c r="D21" t="n">
-        <v>19.20398891061169</v>
+        <v>0.0008055571366914641</v>
       </c>
       <c r="E21" t="n">
-        <v>19.13799925451946</v>
+        <v>0.0006398054177823425</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.417209620603197</v>
+        <v>-0.0002077195107340144</v>
       </c>
       <c r="G21" t="n">
-        <v>33.54876354754175</v>
+        <v>0.0003657614844418206</v>
       </c>
       <c r="H21" t="n">
-        <v>3.864739732323986</v>
+        <v>9.865607519946806e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>-30.47203150179993</v>
+        <v>-0.000562788162212188</v>
       </c>
       <c r="J21" t="n">
-        <v>14.95537091700151</v>
+        <v>0.0001390963805902601</v>
       </c>
       <c r="K21" t="n">
-        <v>25.75452426963503</v>
+        <v>0.0008787053201504831</v>
       </c>
       <c r="L21" t="n">
-        <v>60.31934264278891</v>
+        <v>0.008323717691996821</v>
       </c>
       <c r="M21" t="n">
-        <v>-6.892432044576357</v>
+        <v>-5.720760492086056e-05</v>
       </c>
       <c r="N21" t="n">
-        <v>18.69652603289342</v>
+        <v>0.0001882670534219609</v>
       </c>
       <c r="O21" t="n">
-        <v>-10.57548849228917</v>
+        <v>-0.0001647022884578631</v>
       </c>
       <c r="P21" t="n">
-        <v>34.78342177495396</v>
+        <v>0.0005495707851184971</v>
       </c>
       <c r="Q21" t="n">
-        <v>-26.45804391958276</v>
+        <v>-0.003070462513117117</v>
       </c>
       <c r="R21" t="n">
-        <v>-3.741442212514133</v>
+        <v>-0.0002789479197859808</v>
       </c>
       <c r="S21" t="n">
-        <v>-13.66610902834459</v>
+        <v>-0.002882877865051998</v>
       </c>
       <c r="T21" t="n">
-        <v>-39.5270506142679</v>
+        <v>-0.04364815981198728</v>
       </c>
       <c r="U21" t="n">
-        <v>-87.8222523675837</v>
+        <v>-0.03024460409712461</v>
       </c>
       <c r="V21" t="n">
-        <v>135.0481403676837</v>
+        <v>0.02490919957046209</v>
       </c>
       <c r="W21" t="n">
-        <v>-35.25995853229698</v>
+        <v>-0.01131881626248911</v>
       </c>
       <c r="X21" t="n">
-        <v>118.6355052946844</v>
+        <v>0.056136576302954</v>
       </c>
       <c r="Y21" t="n">
-        <v>43.98912823638202</v>
+        <v>0.02417175592672338</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.203986465423052</v>
+        <v>0.003546278252808014</v>
       </c>
     </row>
     <row r="22">
@@ -2107,79 +2107,79 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3504.251547071507</v>
+        <v>0.07926087393219756</v>
       </c>
       <c r="C22" t="n">
-        <v>-1596.595699500066</v>
+        <v>-0.02209730885322233</v>
       </c>
       <c r="D22" t="n">
-        <v>-1449.989017140334</v>
+        <v>-0.06082324908218418</v>
       </c>
       <c r="E22" t="n">
-        <v>-3071.847153415864</v>
+        <v>-0.1026953980516333</v>
       </c>
       <c r="F22" t="n">
-        <v>-1094.39572734283</v>
+        <v>-0.02413956513569544</v>
       </c>
       <c r="G22" t="n">
-        <v>4962.920972327521</v>
+        <v>0.05410766746838774</v>
       </c>
       <c r="H22" t="n">
-        <v>-581.5013442354129</v>
+        <v>-0.0148441148224445</v>
       </c>
       <c r="I22" t="n">
-        <v>1649.653401430582</v>
+        <v>0.03046746016993855</v>
       </c>
       <c r="J22" t="n">
-        <v>3742.897844824839</v>
+        <v>0.0348118108219146</v>
       </c>
       <c r="K22" t="n">
-        <v>5420.013840938936</v>
+        <v>0.1849226546551849</v>
       </c>
       <c r="L22" t="n">
-        <v>-3193.514999325216</v>
+        <v>-0.440686455370686</v>
       </c>
       <c r="M22" t="n">
-        <v>-688.4770651850887</v>
+        <v>-0.005714401489554764</v>
       </c>
       <c r="N22" t="n">
-        <v>165.1799971008801</v>
+        <v>0.001663301047676936</v>
       </c>
       <c r="O22" t="n">
-        <v>989.7782153713785</v>
+        <v>0.01541477136079969</v>
       </c>
       <c r="P22" t="n">
-        <v>418.43264545098</v>
+        <v>0.006611148235142521</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3946.415366317396</v>
+        <v>-0.4579824752085454</v>
       </c>
       <c r="R22" t="n">
-        <v>13412.6908542093</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.325842782113227</v>
+        <v>-0.001123491275933499</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.06491987484053328</v>
+        <v>-7.168845203418657e-05</v>
       </c>
       <c r="U22" t="n">
-        <v>0.00822571394553418</v>
+        <v>2.83280666336801e-06</v>
       </c>
       <c r="V22" t="n">
-        <v>0.01323318551019917</v>
+        <v>2.440818940039078e-06</v>
       </c>
       <c r="W22" t="n">
-        <v>0.003755286714615033</v>
+        <v>1.205486396042138e-06</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.003641726144627445</v>
+        <v>-1.723211251846888e-06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.001882706474696344</v>
+        <v>1.034535650342426e-06</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.004968651491926349</v>
+        <v>2.14776326190488e-06</v>
       </c>
     </row>
     <row r="23">
@@ -2189,79 +2189,79 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-93.72336633261108</v>
+        <v>-0.002119880899987991</v>
       </c>
       <c r="C23" t="n">
-        <v>-81.05873178368667</v>
+        <v>-0.001121874393145051</v>
       </c>
       <c r="D23" t="n">
-        <v>34.8867722029298</v>
+        <v>0.001463408901921947</v>
       </c>
       <c r="E23" t="n">
-        <v>34.98857546255937</v>
+        <v>0.001169708486436761</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.31956023833075</v>
+        <v>-0.0004040825512944912</v>
       </c>
       <c r="G23" t="n">
-        <v>56.1423519620708</v>
+        <v>0.0006120854488304035</v>
       </c>
       <c r="H23" t="n">
-        <v>6.287830310527101</v>
+        <v>0.0001605108501275017</v>
       </c>
       <c r="I23" t="n">
-        <v>-52.04410200183264</v>
+        <v>-0.0009612028826455154</v>
       </c>
       <c r="J23" t="n">
-        <v>30.37249270941678</v>
+        <v>0.0002824873972588152</v>
       </c>
       <c r="K23" t="n">
-        <v>46.69088098621732</v>
+        <v>0.00159302206849436</v>
       </c>
       <c r="L23" t="n">
-        <v>106.9027056831748</v>
+        <v>0.0147519502638968</v>
       </c>
       <c r="M23" t="n">
-        <v>-16.55241479825022</v>
+        <v>-0.0001373860489505497</v>
       </c>
       <c r="N23" t="n">
-        <v>29.55198302293052</v>
+        <v>0.000297577462075821</v>
       </c>
       <c r="O23" t="n">
-        <v>-16.42627203132759</v>
+        <v>-0.0002558221869716608</v>
       </c>
       <c r="P23" t="n">
-        <v>63.91344565613143</v>
+        <v>0.00100981906656925</v>
       </c>
       <c r="Q23" t="n">
-        <v>-47.03224488267487</v>
+        <v>-0.005458103602024517</v>
       </c>
       <c r="R23" t="n">
-        <v>-6.706136444922702</v>
+        <v>-0.0004999844190711456</v>
       </c>
       <c r="S23" t="n">
-        <v>-23.66058961485855</v>
+        <v>-0.004991222441828959</v>
       </c>
       <c r="T23" t="n">
-        <v>-74.93994259396078</v>
+        <v>-0.0827532168428888</v>
       </c>
       <c r="U23" t="n">
-        <v>209.9900157897443</v>
+        <v>0.07231726266057395</v>
       </c>
       <c r="V23" t="n">
-        <v>35.53595134369649</v>
+        <v>0.006554493098064039</v>
       </c>
       <c r="W23" t="n">
-        <v>-91.72478990831573</v>
+        <v>-0.02944461896450242</v>
       </c>
       <c r="X23" t="n">
-        <v>-176.467976781809</v>
+        <v>-0.08350205125382311</v>
       </c>
       <c r="Y23" t="n">
-        <v>-1.284767427520515</v>
+        <v>-0.0007059718145299702</v>
       </c>
       <c r="Z23" t="n">
-        <v>240.2331470866822</v>
+        <v>0.1038438555094811</v>
       </c>
     </row>
     <row r="24">
@@ -2271,79 +2271,79 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-112.1717666463374</v>
+        <v>-0.002537155833558032</v>
       </c>
       <c r="C24" t="n">
-        <v>-94.97177152104575</v>
+        <v>-0.001314434561169959</v>
       </c>
       <c r="D24" t="n">
-        <v>41.89031661041338</v>
+        <v>0.001757189282958643</v>
       </c>
       <c r="E24" t="n">
-        <v>42.1235315415673</v>
+        <v>0.001408238308403929</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.60389566931734</v>
+        <v>-0.0004985840114295515</v>
       </c>
       <c r="G24" t="n">
-        <v>65.00826720565406</v>
+        <v>0.0007087450564440495</v>
       </c>
       <c r="H24" t="n">
-        <v>7.183272034412497</v>
+        <v>0.0001833689912099432</v>
       </c>
       <c r="I24" t="n">
-        <v>-60.83370752667573</v>
+        <v>-0.001123538168351831</v>
       </c>
       <c r="J24" t="n">
-        <v>38.07348010126053</v>
+        <v>0.0003541124662137389</v>
       </c>
       <c r="K24" t="n">
-        <v>56.01619817911672</v>
+        <v>0.001911187752461295</v>
       </c>
       <c r="L24" t="n">
-        <v>127.0238693353079</v>
+        <v>0.01752855356454378</v>
       </c>
       <c r="M24" t="n">
-        <v>-21.89340229514957</v>
+        <v>-0.0001817165698223959</v>
       </c>
       <c r="N24" t="n">
-        <v>33.27582319369868</v>
+        <v>0.0003350751456097259</v>
       </c>
       <c r="O24" t="n">
-        <v>-18.3297208326507</v>
+        <v>-0.0002854664321305368</v>
       </c>
       <c r="P24" t="n">
-        <v>77.10674797640414</v>
+        <v>0.001218270482343383</v>
       </c>
       <c r="Q24" t="n">
-        <v>-55.95699552154182</v>
+        <v>-0.006493823111707421</v>
       </c>
       <c r="R24" t="n">
-        <v>-8.00701340970347</v>
+        <v>-0.0005969729338233897</v>
       </c>
       <c r="S24" t="n">
-        <v>-32.2074910100654</v>
+        <v>-0.006794198899569727</v>
       </c>
       <c r="T24" t="n">
-        <v>54.50328036280993</v>
+        <v>0.06018581843530595</v>
       </c>
       <c r="U24" t="n">
-        <v>-131.7321833871133</v>
+        <v>-0.04536649454989006</v>
       </c>
       <c r="V24" t="n">
-        <v>-321.7898481669338</v>
+        <v>-0.05935311308927081</v>
       </c>
       <c r="W24" t="n">
-        <v>-244.4148897214524</v>
+        <v>-0.07845974141006561</v>
       </c>
       <c r="X24" t="n">
-        <v>-31.00854761029636</v>
+        <v>-0.01467278867861137</v>
       </c>
       <c r="Y24" t="n">
-        <v>-22.47414618129602</v>
+        <v>-0.01234940536299361</v>
       </c>
       <c r="Z24" t="n">
-        <v>-168.7236249203657</v>
+        <v>-0.07293294842840463</v>
       </c>
     </row>
     <row r="25">
@@ -2353,79 +2353,79 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-2270.407371675436</v>
+        <v>-0.05135318342414266</v>
       </c>
       <c r="C25" t="n">
-        <v>999.3573257435809</v>
+        <v>0.01383137101559337</v>
       </c>
       <c r="D25" t="n">
-        <v>1019.811616416179</v>
+        <v>0.04277843158048065</v>
       </c>
       <c r="E25" t="n">
-        <v>1332.739466441211</v>
+        <v>0.04455501955984612</v>
       </c>
       <c r="F25" t="n">
-        <v>-1587.850743318358</v>
+        <v>-0.03502391821024412</v>
       </c>
       <c r="G25" t="n">
-        <v>-2753.49997127555</v>
+        <v>-0.03001971251420535</v>
       </c>
       <c r="H25" t="n">
-        <v>174.4717011876041</v>
+        <v>0.004453778123421746</v>
       </c>
       <c r="I25" t="n">
-        <v>-476.7390786180101</v>
+        <v>-0.008804897366108115</v>
       </c>
       <c r="J25" t="n">
-        <v>-2560.154249564945</v>
+        <v>-0.0238113913619105</v>
       </c>
       <c r="K25" t="n">
-        <v>-6170.609532689884</v>
+        <v>-0.210531841636022</v>
       </c>
       <c r="L25" t="n">
-        <v>4001.993981630476</v>
+        <v>0.552251842421972</v>
       </c>
       <c r="M25" t="n">
-        <v>2780.106177084145</v>
+        <v>0.02307505025629155</v>
       </c>
       <c r="N25" t="n">
-        <v>-2281.60754813587</v>
+        <v>-0.02297493819959498</v>
       </c>
       <c r="O25" t="n">
-        <v>1628.890729285094</v>
+        <v>0.02536828733317267</v>
       </c>
       <c r="P25" t="n">
-        <v>-1093.853070626956</v>
+        <v>-0.01728264961159159</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1553.5895706466</v>
+        <v>-0.1802944523011181</v>
       </c>
       <c r="R25" t="n">
-        <v>5871.512306928808</v>
+        <v>0.4377579689824996</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.490419549108744</v>
+        <v>-0.0005253562208473067</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.02810018625991078</v>
+        <v>-3.102992511605363e-05</v>
       </c>
       <c r="U25" t="n">
-        <v>0.003093723413804956</v>
+        <v>1.065429743761309e-06</v>
       </c>
       <c r="V25" t="n">
-        <v>0.00478312624809874</v>
+        <v>8.82232409570577e-07</v>
       </c>
       <c r="W25" t="n">
-        <v>0.001603513834870924</v>
+        <v>5.147447480585829e-07</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.001556405572748959</v>
+        <v>-7.36468226572973e-07</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.0006468999691304177</v>
+        <v>3.554675618666322e-07</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.001801075194599523</v>
+        <v>7.785378268479247e-07</v>
       </c>
     </row>
     <row r="26">
@@ -2435,79 +2435,79 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-1168.518640941312</v>
+        <v>-0.02643012564679401</v>
       </c>
       <c r="C26" t="n">
-        <v>295.1688852066874</v>
+        <v>0.004085215826596451</v>
       </c>
       <c r="D26" t="n">
-        <v>-247.6263401532408</v>
+        <v>-0.01038727768859545</v>
       </c>
       <c r="E26" t="n">
-        <v>-1295.345950882481</v>
+        <v>-0.04330491114850038</v>
       </c>
       <c r="F26" t="n">
-        <v>565.9376706615446</v>
+        <v>0.01248313468551994</v>
       </c>
       <c r="G26" t="n">
-        <v>590.8213731577656</v>
+        <v>0.006441361160148437</v>
       </c>
       <c r="H26" t="n">
-        <v>248.3380009560848</v>
+        <v>0.006339379672140676</v>
       </c>
       <c r="I26" t="n">
-        <v>1876.328306349555</v>
+        <v>0.0346539205689256</v>
       </c>
       <c r="J26" t="n">
-        <v>-877.7455242490166</v>
+        <v>-0.008163704275869434</v>
       </c>
       <c r="K26" t="n">
-        <v>338.7505025761755</v>
+        <v>0.01155765354859546</v>
       </c>
       <c r="L26" t="n">
-        <v>1190.214178639172</v>
+        <v>0.1642426190662193</v>
       </c>
       <c r="M26" t="n">
-        <v>-276.130047872985</v>
+        <v>-0.002291896181686182</v>
       </c>
       <c r="N26" t="n">
-        <v>846.5014839920156</v>
+        <v>0.008523954654897489</v>
       </c>
       <c r="O26" t="n">
-        <v>810.6916353686815</v>
+        <v>0.01262568321796425</v>
       </c>
       <c r="P26" t="n">
-        <v>595.7729989899009</v>
+        <v>0.009413088710065952</v>
       </c>
       <c r="Q26" t="n">
-        <v>168.8158957251394</v>
+        <v>0.01959112627591794</v>
       </c>
       <c r="R26" t="n">
-        <v>-35.46987183599975</v>
+        <v>-0.00264450081057883</v>
       </c>
       <c r="S26" t="n">
-        <v>4740.439820227382</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>107.4259840915984</v>
+        <v>0.118626268560942</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.612038040742203</v>
+        <v>-0.001243929158964786</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.569250337319652</v>
+        <v>-0.0004738900456128506</v>
       </c>
       <c r="W26" t="n">
-        <v>-5.209227441932021</v>
+        <v>-0.001672216608840794</v>
       </c>
       <c r="X26" t="n">
-        <v>3.658188935738599</v>
+        <v>0.001731001202478238</v>
       </c>
       <c r="Y26" t="n">
-        <v>-0.9008081868200726</v>
+        <v>-0.0004949885688027876</v>
       </c>
       <c r="Z26" t="n">
-        <v>-0.6410007374810657</v>
+        <v>-0.0002770807807818321</v>
       </c>
     </row>
     <row r="27">
@@ -2517,79 +2517,79 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>16.13731625351961</v>
+        <v>0.0003650017049270124</v>
       </c>
       <c r="C27" t="n">
-        <v>-266.3278630758346</v>
+        <v>-0.003686048414415877</v>
       </c>
       <c r="D27" t="n">
-        <v>-116.5540083934246</v>
+        <v>-0.004889135986713572</v>
       </c>
       <c r="E27" t="n">
-        <v>-148.5030134160399</v>
+        <v>-0.004964627246400836</v>
       </c>
       <c r="F27" t="n">
-        <v>63.42752637190058</v>
+        <v>0.001399048685952058</v>
       </c>
       <c r="G27" t="n">
-        <v>-136.5747276588772</v>
+        <v>-0.001488990050407046</v>
       </c>
       <c r="H27" t="n">
-        <v>-137.8292895318646</v>
+        <v>-0.003518399088822517</v>
       </c>
       <c r="I27" t="n">
-        <v>2.741235105133693</v>
+        <v>5.062789026450693e-05</v>
       </c>
       <c r="J27" t="n">
-        <v>51.69426941436822</v>
+        <v>0.0004807962178070852</v>
       </c>
       <c r="K27" t="n">
-        <v>-83.78586112122133</v>
+        <v>-0.002858646548847707</v>
       </c>
       <c r="L27" t="n">
-        <v>25.48533568738873</v>
+        <v>0.003516827774530724</v>
       </c>
       <c r="M27" t="n">
-        <v>-55.96353190329292</v>
+        <v>-0.0004645007164951076</v>
       </c>
       <c r="N27" t="n">
-        <v>-45.33299567335975</v>
+        <v>-0.0004564863816517862</v>
       </c>
       <c r="O27" t="n">
-        <v>3.127022703024298</v>
+        <v>4.870014237387836e-05</v>
       </c>
       <c r="P27" t="n">
-        <v>13.02543177989994</v>
+        <v>0.0002057990963655418</v>
       </c>
       <c r="Q27" t="n">
-        <v>36.64952294863902</v>
+        <v>0.004253186164459137</v>
       </c>
       <c r="R27" t="n">
-        <v>0.199514438002422</v>
+        <v>1.487504932239667e-05</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.001310044242431121</v>
+        <v>-2.763549991376714e-07</v>
       </c>
       <c r="T27" t="n">
-        <v>0.0002344433703978148</v>
+        <v>2.588865482994317e-07</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.099862487078671e-06</v>
+        <v>-2.789465398103017e-09</v>
       </c>
       <c r="V27" t="n">
-        <v>-7.346818888859188e-06</v>
+        <v>-1.355097355745787e-09</v>
       </c>
       <c r="W27" t="n">
-        <v>-1.060755839214962e-05</v>
+        <v>-3.405137425910194e-09</v>
       </c>
       <c r="X27" t="n">
-        <v>5.204939363376642e-06</v>
+        <v>2.462900756385396e-09</v>
       </c>
       <c r="Y27" t="n">
-        <v>-4.034600103973962e-06</v>
+        <v>-2.216987989649062e-09</v>
       </c>
       <c r="Z27" t="n">
-        <v>-1.434595877796983e-06</v>
+        <v>-6.201224471104876e-10</v>
       </c>
     </row>
     <row r="28">
@@ -2599,79 +2599,79 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-221.6933851667293</v>
+        <v>-0.005014369321741984</v>
       </c>
       <c r="C28" t="n">
-        <v>-147.4785786502197</v>
+        <v>-0.00204114272804855</v>
       </c>
       <c r="D28" t="n">
-        <v>7.868296062171432</v>
+        <v>0.0003300544525403837</v>
       </c>
       <c r="E28" t="n">
-        <v>-14.09945301959755</v>
+        <v>-0.0004713609980717197</v>
       </c>
       <c r="F28" t="n">
-        <v>-95.78391930314615</v>
+        <v>-0.002112747794241139</v>
       </c>
       <c r="G28" t="n">
-        <v>-19.13072832880508</v>
+        <v>-0.000208570535903093</v>
       </c>
       <c r="H28" t="n">
-        <v>206.9205031842393</v>
+        <v>0.00528210594667407</v>
       </c>
       <c r="I28" t="n">
-        <v>-24.18249841454939</v>
+        <v>-0.0004466267317825365</v>
       </c>
       <c r="J28" t="n">
-        <v>47.98269322674901</v>
+        <v>0.0004462757223377332</v>
       </c>
       <c r="K28" t="n">
-        <v>-29.09051491277584</v>
+        <v>-0.0009925242630053573</v>
       </c>
       <c r="L28" t="n">
-        <v>-206.6576186337194</v>
+        <v>-0.02851754679413876</v>
       </c>
       <c r="M28" t="n">
-        <v>-19.42310338003316</v>
+        <v>-0.000161212938671819</v>
       </c>
       <c r="N28" t="n">
-        <v>81.14856065899501</v>
+        <v>0.0008171357811512073</v>
       </c>
       <c r="O28" t="n">
-        <v>194.4310532291585</v>
+        <v>0.003028062432999089</v>
       </c>
       <c r="P28" t="n">
-        <v>-158.8573849469044</v>
+        <v>-0.002509913438993657</v>
       </c>
       <c r="Q28" t="n">
-        <v>-11.54491533014373</v>
+        <v>-0.001339790267415826</v>
       </c>
       <c r="R28" t="n">
-        <v>-16.4293530471303</v>
+        <v>-0.001224911035802654</v>
       </c>
       <c r="S28" t="n">
-        <v>1.724121185557434</v>
+        <v>0.0003637048989000211</v>
       </c>
       <c r="T28" t="n">
-        <v>-156.1020549678516</v>
+        <v>-0.1723773298622222</v>
       </c>
       <c r="U28" t="n">
-        <v>482.6741732492983</v>
+        <v>0.1662254028367459</v>
       </c>
       <c r="V28" t="n">
-        <v>39.88199090084156</v>
+        <v>0.007356106258936223</v>
       </c>
       <c r="W28" t="n">
-        <v>-62.09194757486971</v>
+        <v>-0.01993216598188303</v>
       </c>
       <c r="X28" t="n">
-        <v>60.86095784476218</v>
+        <v>0.02879851015458558</v>
       </c>
       <c r="Y28" t="n">
-        <v>526.9885218395628</v>
+        <v>0.2895769576891785</v>
       </c>
       <c r="Z28" t="n">
-        <v>-468.2794820296248</v>
+        <v>-0.2024198053418199</v>
       </c>
     </row>
   </sheetData>
